--- a/grupos/5ALCV - Estadisticos 20241.xlsx
+++ b/grupos/5ALCV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -185,12 +185,12 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
-    <t>Flores Ovalle Victor</t>
-  </si>
-  <si>
     <t>Marin Arzaba Roberto</t>
   </si>
   <si>
@@ -206,94 +206,91 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>BONILLA</t>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>IBAÑEZ</t>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>FERNANDA MARGARITA</t>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>PULIDO</t>
+  </si>
+  <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>JARET</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
   </si>
   <si>
     <t>AILYN</t>
   </si>
   <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
     <t>AZURA</t>
   </si>
   <si>
-    <t>ANA SHECIT</t>
-  </si>
-  <si>
     <t>KEVIN ALEXIS</t>
   </si>
   <si>
     <t>MARIA ANGELES</t>
   </si>
   <si>
+    <t>NOEMI DEL ROCIO</t>
+  </si>
+  <si>
     <t>KAREN</t>
   </si>
   <si>
     <t>JUAN EMANUEL</t>
-  </si>
-  <si>
-    <t>BRENDA JANELY</t>
   </si>
 </sst>
 </file>
@@ -801,22 +798,22 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -843,10 +840,10 @@
         <v>5</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -878,22 +875,22 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -955,22 +952,22 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1032,22 +1029,22 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1068,7 +1065,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -1083,7 +1080,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1109,22 +1106,22 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1145,7 +1142,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>6</v>
@@ -1154,10 +1151,10 @@
         <v>10</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1177,7 +1174,7 @@
         <v>6</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -1186,22 +1183,22 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1228,10 +1225,10 @@
         <v>5</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1263,22 +1260,22 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1305,10 +1302,10 @@
         <v>8</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1340,22 +1337,22 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1382,16 +1379,16 @@
         <v>6</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1417,22 +1414,22 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1453,22 +1450,22 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>5</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>10</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1494,22 +1491,22 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1530,22 +1527,22 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>6</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1571,22 +1568,22 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I14">
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1613,13 +1610,13 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1648,22 +1645,22 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1684,22 +1681,22 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>6</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1725,22 +1722,22 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1761,22 +1758,22 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>5</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1802,22 +1799,22 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1838,22 +1835,22 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U17">
         <v>5</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1879,22 +1876,22 @@
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1921,10 +1918,10 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -1956,22 +1953,22 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1992,7 +1989,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>5</v>
@@ -2007,7 +2004,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2033,22 +2030,22 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2069,22 +2066,22 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>6</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2110,22 +2107,22 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2146,13 +2143,13 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>5</v>
       </c>
       <c r="V21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2187,22 +2184,22 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2223,22 +2220,22 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>6</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>7</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2264,22 +2261,22 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2300,7 +2297,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>8</v>
@@ -2309,13 +2306,13 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2341,22 +2338,22 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2377,22 +2374,22 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>8</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2418,22 +2415,22 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2454,7 +2451,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U25">
         <v>7</v>
@@ -2463,13 +2460,13 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2495,22 +2492,22 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2531,22 +2528,22 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>5</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2563,7 +2560,7 @@
         <v>5</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F27">
         <v>6</v>
@@ -2572,22 +2569,22 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I27">
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2608,19 +2605,19 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>5</v>
       </c>
       <c r="V27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2649,22 +2646,22 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2685,22 +2682,22 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U28">
         <v>8</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2726,22 +2723,22 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2762,22 +2759,22 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>5</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2803,22 +2800,22 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I30">
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2839,19 +2836,19 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>8</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -2880,22 +2877,22 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2916,7 +2913,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>8</v>
@@ -2925,13 +2922,13 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3073,10 +3070,10 @@
         <v>83.3</v>
       </c>
       <c r="J4">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K4">
-        <v>78.3</v>
+        <v>85.7</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -3091,10 +3088,10 @@
         <v>83.3</v>
       </c>
       <c r="P4">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q4">
-        <v>78.3</v>
+        <v>85.7</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -3132,7 +3129,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="J5">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K5">
         <v>100</v>
@@ -3150,7 +3147,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="P5">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -3244,16 +3241,16 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="I7">
         <v>77.8</v>
       </c>
       <c r="J7">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K7">
-        <v>78.3</v>
+        <v>51.4</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -3262,16 +3259,16 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O7">
         <v>77.8</v>
       </c>
       <c r="P7">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q7">
-        <v>78.3</v>
+        <v>51.4</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -3309,7 +3306,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -3327,7 +3324,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3362,7 +3359,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>78.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="I9">
         <v>83.3</v>
@@ -3377,10 +3374,10 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N9">
-        <v>78.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="O9">
         <v>83.3</v>
@@ -3395,7 +3392,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3421,16 +3418,16 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="I10">
         <v>83.3</v>
       </c>
       <c r="J10">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K10">
-        <v>78.3</v>
+        <v>85.7</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -3439,16 +3436,16 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O10">
         <v>83.3</v>
       </c>
       <c r="P10">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="Q10">
-        <v>78.3</v>
+        <v>85.7</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -3486,7 +3483,7 @@
         <v>83.3</v>
       </c>
       <c r="J11">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -3504,7 +3501,7 @@
         <v>83.3</v>
       </c>
       <c r="P11">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -3545,7 +3542,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="J12">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -3563,7 +3560,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="P12">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -3604,7 +3601,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="J13">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -3622,7 +3619,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="P13">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -3663,7 +3660,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="J14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -3681,7 +3678,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="P14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -3722,7 +3719,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="J15">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -3740,7 +3737,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="P15">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -3781,7 +3778,7 @@
         <v>83.3</v>
       </c>
       <c r="J16">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K16">
         <v>100</v>
@@ -3799,7 +3796,7 @@
         <v>83.3</v>
       </c>
       <c r="P16">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -3840,7 +3837,7 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -3858,7 +3855,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -3952,16 +3949,16 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="I19">
         <v>77.8</v>
       </c>
       <c r="J19">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K19">
-        <v>78.3</v>
+        <v>51.4</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -3970,16 +3967,16 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O19">
         <v>77.8</v>
       </c>
       <c r="P19">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q19">
-        <v>78.3</v>
+        <v>51.4</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -4070,16 +4067,16 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I21">
         <v>88.90000000000001</v>
       </c>
       <c r="J21">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K21">
-        <v>78.3</v>
+        <v>51.4</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -4088,16 +4085,16 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O21">
         <v>88.90000000000001</v>
       </c>
       <c r="P21">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q21">
-        <v>78.3</v>
+        <v>51.4</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -4135,7 +4132,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="J22">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -4153,7 +4150,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="P22">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4194,7 +4191,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="J23">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K23">
         <v>100</v>
@@ -4212,7 +4209,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="P23">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -4312,7 +4309,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="J25">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -4330,7 +4327,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="P25">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -4374,7 +4371,7 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>78.3</v>
+        <v>85.7</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -4392,7 +4389,7 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>78.3</v>
+        <v>85.7</v>
       </c>
       <c r="R26">
         <v>100</v>
@@ -4424,13 +4421,13 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="I27">
         <v>66.7</v>
       </c>
       <c r="J27">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -4442,13 +4439,13 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O27">
         <v>66.7</v>
       </c>
       <c r="P27">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4548,7 +4545,7 @@
         <v>83.3</v>
       </c>
       <c r="J29">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -4566,7 +4563,7 @@
         <v>83.3</v>
       </c>
       <c r="P29">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -4601,16 +4598,16 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="I30">
         <v>83.3</v>
       </c>
       <c r="J30">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K30">
-        <v>78.3</v>
+        <v>85.7</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -4619,16 +4616,16 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O30">
         <v>83.3</v>
       </c>
       <c r="P30">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q30">
-        <v>78.3</v>
+        <v>85.7</v>
       </c>
       <c r="R30">
         <v>100</v>
@@ -4666,10 +4663,10 @@
         <v>94.40000000000001</v>
       </c>
       <c r="J31">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K31">
-        <v>82.59999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -4684,10 +4681,10 @@
         <v>94.40000000000001</v>
       </c>
       <c r="P31">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q31">
-        <v>82.59999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -4791,25 +4788,25 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>64.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>28.6</v>
+        <v>21.4</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>7.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4823,19 +4820,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>82.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="G4" s="2">
-        <v>17.9</v>
+        <v>14.3</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4846,7 +4843,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -4855,19 +4852,19 @@
         <v>28</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>82.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="G5" s="2">
-        <v>17.9</v>
+        <v>10.7</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4878,7 +4875,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -4887,19 +4884,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>89.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4919,19 +4916,19 @@
         <v>28</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>92.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4947,7 +4944,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4974,46 +4971,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920233</v>
-      </c>
-      <c r="B2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920366</v>
-      </c>
-      <c r="B3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>53</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5021,7 +4978,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5056,13 +5013,13 @@
         <v>22330051920231</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -5079,13 +5036,13 @@
         <v>22330051920231</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5099,16 +5056,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920230</v>
+        <v>22330051920357</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5122,22 +5079,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920230</v>
+        <v>22330051920357</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5145,22 +5102,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920234</v>
+        <v>22330051920369</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5168,22 +5125,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920236</v>
+        <v>22330051920369</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5191,16 +5148,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920243</v>
+        <v>22330051920366</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5214,22 +5171,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920257</v>
+        <v>22330051920366</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5237,22 +5194,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920401</v>
+        <v>22330051920230</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5260,24 +5217,116 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920259</v>
+        <v>22330051920236</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920243</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920253</v>
+      </c>
+      <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920257</v>
+      </c>
+      <c r="B14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920401</v>
+      </c>
+      <c r="B15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCV - Estadisticos 20241.xlsx
+++ b/grupos/5ALCV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="83">
   <si>
     <t>Materia</t>
   </si>
@@ -179,7 +179,7 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
+    <t>Urias Morales Alejandra</t>
   </si>
   <si>
     <t>Jiménez Nieto Enrique</t>
@@ -218,12 +218,6 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
@@ -245,15 +239,6 @@
     <t>FLORES</t>
   </si>
   <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -273,15 +258,6 @@
   </si>
   <si>
     <t>AILYN</t>
-  </si>
-  <si>
-    <t>AZURA</t>
-  </si>
-  <si>
-    <t>KEVIN ALEXIS</t>
-  </si>
-  <si>
-    <t>MARIA ANGELES</t>
   </si>
   <si>
     <t>NOEMI DEL ROCIO</t>
@@ -801,7 +777,7 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -837,7 +813,7 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -878,7 +854,7 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -914,7 +890,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -955,7 +931,7 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -1032,7 +1008,7 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1068,7 +1044,7 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>6</v>
@@ -1109,7 +1085,7 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>9</v>
@@ -1145,7 +1121,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1186,7 +1162,7 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -1263,7 +1239,7 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>9</v>
@@ -1299,7 +1275,7 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1340,7 +1316,7 @@
         <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>10</v>
@@ -1376,7 +1352,7 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>10</v>
@@ -1417,7 +1393,7 @@
         <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>9</v>
@@ -1453,7 +1429,7 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1494,7 +1470,7 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>9</v>
@@ -1530,7 +1506,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -1571,7 +1547,7 @@
         <v>5</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>7</v>
@@ -1648,7 +1624,7 @@
         <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>9</v>
@@ -1684,7 +1660,7 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>9</v>
@@ -1725,7 +1701,7 @@
         <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>7</v>
@@ -1802,7 +1778,7 @@
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>10</v>
@@ -1838,7 +1814,7 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>10</v>
@@ -1879,7 +1855,7 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>10</v>
@@ -1956,7 +1932,7 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>6</v>
@@ -2033,7 +2009,7 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>10</v>
@@ -2069,7 +2045,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -2110,7 +2086,7 @@
         <v>5</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>7</v>
@@ -2187,7 +2163,7 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>10</v>
@@ -2223,7 +2199,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2264,7 +2240,7 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>9</v>
@@ -2341,7 +2317,7 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>9</v>
@@ -2418,7 +2394,7 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>10</v>
@@ -2454,7 +2430,7 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2495,7 +2471,7 @@
         <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>7</v>
@@ -2572,7 +2548,7 @@
         <v>7</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>7</v>
@@ -2649,7 +2625,7 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
         <v>9</v>
@@ -2726,7 +2702,7 @@
         <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
         <v>9</v>
@@ -2803,7 +2779,7 @@
         <v>5</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
         <v>7</v>
@@ -2839,7 +2815,7 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>7</v>
@@ -2880,7 +2856,7 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>8</v>
@@ -2916,7 +2892,7 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3067,7 +3043,7 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>83.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="J4">
         <v>98</v>
@@ -3085,7 +3061,7 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>83.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="P4">
         <v>98</v>
@@ -3126,7 +3102,7 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>94.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="J5">
         <v>98</v>
@@ -3144,7 +3120,7 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>94.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P5">
         <v>98</v>
@@ -3185,7 +3161,7 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>83.3</v>
+        <v>89.5</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3203,7 +3179,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>83.3</v>
+        <v>89.5</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3244,7 +3220,7 @@
         <v>93.8</v>
       </c>
       <c r="I7">
-        <v>77.8</v>
+        <v>76.3</v>
       </c>
       <c r="J7">
         <v>90</v>
@@ -3262,7 +3238,7 @@
         <v>93.8</v>
       </c>
       <c r="O7">
-        <v>77.8</v>
+        <v>76.3</v>
       </c>
       <c r="P7">
         <v>90</v>
@@ -3362,7 +3338,7 @@
         <v>82.8</v>
       </c>
       <c r="I9">
-        <v>83.3</v>
+        <v>76.3</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -3380,7 +3356,7 @@
         <v>82.8</v>
       </c>
       <c r="O9">
-        <v>83.3</v>
+        <v>76.3</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3421,7 +3397,7 @@
         <v>93.8</v>
       </c>
       <c r="I10">
-        <v>83.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="J10">
         <v>92</v>
@@ -3439,7 +3415,7 @@
         <v>93.8</v>
       </c>
       <c r="O10">
-        <v>83.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="P10">
         <v>92</v>
@@ -3480,7 +3456,7 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>83.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="J11">
         <v>98</v>
@@ -3498,7 +3474,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>83.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="P11">
         <v>98</v>
@@ -3539,7 +3515,7 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="J12">
         <v>96</v>
@@ -3557,7 +3533,7 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="P12">
         <v>96</v>
@@ -3598,7 +3574,7 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>88.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="J13">
         <v>96</v>
@@ -3616,7 +3592,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>88.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="P13">
         <v>96</v>
@@ -3657,7 +3633,7 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>88.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="J14">
         <v>96</v>
@@ -3675,7 +3651,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>88.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="P14">
         <v>96</v>
@@ -3716,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="J15">
         <v>98</v>
@@ -3734,7 +3710,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="P15">
         <v>98</v>
@@ -3775,7 +3751,7 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>83.3</v>
+        <v>86.8</v>
       </c>
       <c r="J16">
         <v>96</v>
@@ -3793,7 +3769,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>83.3</v>
+        <v>86.8</v>
       </c>
       <c r="P16">
         <v>96</v>
@@ -3952,7 +3928,7 @@
         <v>93.8</v>
       </c>
       <c r="I19">
-        <v>77.8</v>
+        <v>76.3</v>
       </c>
       <c r="J19">
         <v>90</v>
@@ -3970,7 +3946,7 @@
         <v>93.8</v>
       </c>
       <c r="O19">
-        <v>77.8</v>
+        <v>76.3</v>
       </c>
       <c r="P19">
         <v>90</v>
@@ -4070,7 +4046,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="I21">
-        <v>88.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J21">
         <v>90</v>
@@ -4088,7 +4064,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="O21">
-        <v>88.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="P21">
         <v>90</v>
@@ -4129,7 +4105,7 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>94.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="J22">
         <v>94</v>
@@ -4147,7 +4123,7 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>94.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="P22">
         <v>94</v>
@@ -4188,7 +4164,7 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>94.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="J23">
         <v>96</v>
@@ -4206,7 +4182,7 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>94.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P23">
         <v>96</v>
@@ -4306,7 +4282,7 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="J25">
         <v>98</v>
@@ -4324,7 +4300,7 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="P25">
         <v>98</v>
@@ -4365,7 +4341,7 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>88.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -4383,7 +4359,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>88.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -4424,7 +4400,7 @@
         <v>93.8</v>
       </c>
       <c r="I27">
-        <v>66.7</v>
+        <v>76.3</v>
       </c>
       <c r="J27">
         <v>90</v>
@@ -4442,7 +4418,7 @@
         <v>93.8</v>
       </c>
       <c r="O27">
-        <v>66.7</v>
+        <v>76.3</v>
       </c>
       <c r="P27">
         <v>90</v>
@@ -4542,7 +4518,7 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>83.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="J29">
         <v>98</v>
@@ -4560,7 +4536,7 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>83.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="P29">
         <v>98</v>
@@ -4601,7 +4577,7 @@
         <v>93.8</v>
       </c>
       <c r="I30">
-        <v>83.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="J30">
         <v>98</v>
@@ -4619,7 +4595,7 @@
         <v>93.8</v>
       </c>
       <c r="O30">
-        <v>83.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="P30">
         <v>98</v>
@@ -4660,7 +4636,7 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>94.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="J31">
         <v>90</v>
@@ -4678,7 +4654,7 @@
         <v>100</v>
       </c>
       <c r="O31">
-        <v>94.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P31">
         <v>90</v>
@@ -4756,19 +4732,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>64.3</v>
+        <v>75</v>
       </c>
       <c r="G2" s="2">
-        <v>35.7</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4978,7 +4954,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5016,10 +4992,10 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -5039,10 +5015,10 @@
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5062,10 +5038,10 @@
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5085,10 +5061,10 @@
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5108,10 +5084,10 @@
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5131,10 +5107,10 @@
         <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -5154,10 +5130,10 @@
         <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5177,10 +5153,10 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -5194,16 +5170,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920230</v>
+        <v>22330051920253</v>
       </c>
       <c r="B10" t="s">
         <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5217,16 +5193,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920236</v>
+        <v>22330051920257</v>
       </c>
       <c r="B11" t="s">
         <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -5240,93 +5216,24 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920243</v>
+        <v>22330051920401</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920253</v>
-      </c>
-      <c r="B13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920257</v>
-      </c>
-      <c r="B14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920401</v>
-      </c>
-      <c r="B15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCV - Estadisticos 20241.xlsx
+++ b/grupos/5ALCV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="89">
   <si>
     <t>Materia</t>
   </si>
@@ -206,6 +206,12 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
     <t>ARELLANO</t>
   </si>
   <si>
@@ -227,6 +233,12 @@
     <t>VALENTE</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>FIERROS</t>
   </si>
   <si>
@@ -246,6 +258,12 @@
   </si>
   <si>
     <t>PULIDO</t>
+  </si>
+  <si>
+    <t>CRHIS AMINADAB</t>
+  </si>
+  <si>
+    <t>SERGIO</t>
   </si>
   <si>
     <t>ALDO EMANUEL</t>
@@ -4954,7 +4972,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4986,22 +5004,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920231</v>
+        <v>22330051920239</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5009,22 +5027,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920231</v>
+        <v>22330051920239</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5032,22 +5050,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920357</v>
+        <v>22330051920239</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5055,22 +5073,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920357</v>
+        <v>21330051420317</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5078,22 +5096,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920369</v>
+        <v>21330051420317</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5101,22 +5119,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920369</v>
+        <v>21330051420317</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5124,22 +5142,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920366</v>
+        <v>22330051920231</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5147,22 +5165,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920366</v>
+        <v>22330051920231</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5170,16 +5188,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920253</v>
+        <v>22330051920357</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5193,22 +5211,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920257</v>
+        <v>22330051920357</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
         <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5216,24 +5234,162 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920401</v>
+        <v>22330051920369</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
         <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920369</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920366</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920366</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920253</v>
+      </c>
+      <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920257</v>
+      </c>
+      <c r="B17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920401</v>
+      </c>
+      <c r="B18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
         <v>54</v>
       </c>
-      <c r="G12">
+      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCV - Estadisticos 20241.xlsx
+++ b/grupos/5ALCV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="89">
   <si>
     <t>Materia</t>
   </si>
@@ -179,6 +179,9 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Rivera Serra Alma Lilian</t>
+  </si>
+  <si>
     <t>Urias Morales Alejandra</t>
   </si>
   <si>
@@ -188,9 +191,6 @@
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
-    <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
     <t>Marin Arzaba Roberto</t>
   </si>
   <si>
@@ -206,24 +206,24 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>GAMBOA</t>
   </si>
   <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
@@ -233,24 +233,24 @@
     <t>VALENTE</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -260,22 +260,22 @@
     <t>PULIDO</t>
   </si>
   <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
     <t>CRHIS AMINADAB</t>
   </si>
   <si>
-    <t>SERGIO</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
     <t>JARET</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>AILYN</t>
   </si>
   <si>
     <t>NOEMI DEL ROCIO</t>
@@ -810,7 +810,7 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -819,7 +819,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -837,7 +837,7 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -887,7 +887,7 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -896,7 +896,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -973,7 +973,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -991,7 +991,7 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1041,7 +1041,7 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1050,7 +1050,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1059,7 +1059,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>6</v>
@@ -1118,7 +1118,7 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1127,7 +1127,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1195,7 +1195,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1204,7 +1204,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1272,7 +1272,7 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1281,7 +1281,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1299,7 +1299,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1349,7 +1349,7 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1358,7 +1358,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1426,7 +1426,7 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1435,7 +1435,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1503,7 +1503,7 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1512,7 +1512,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1580,7 +1580,7 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1589,7 +1589,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1607,7 +1607,7 @@
         <v>7</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1657,7 +1657,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1666,7 +1666,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1684,7 +1684,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -1734,7 +1734,7 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1743,7 +1743,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1761,7 +1761,7 @@
         <v>7</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -1811,7 +1811,7 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -1820,7 +1820,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -1888,7 +1888,7 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -1897,7 +1897,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -1965,7 +1965,7 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -1974,7 +1974,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -1983,7 +1983,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>5</v>
@@ -2042,7 +2042,7 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2051,7 +2051,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2119,7 +2119,7 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2128,7 +2128,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2137,7 +2137,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -2196,7 +2196,7 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2205,7 +2205,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2223,7 +2223,7 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2273,7 +2273,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2282,7 +2282,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2300,7 +2300,7 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>9</v>
@@ -2350,7 +2350,7 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2359,7 +2359,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2377,7 +2377,7 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2427,7 +2427,7 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2436,7 +2436,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2504,7 +2504,7 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2513,7 +2513,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2581,7 +2581,7 @@
         <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2590,7 +2590,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2599,7 +2599,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <v>5</v>
@@ -2658,7 +2658,7 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -2667,7 +2667,7 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -2735,7 +2735,7 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -2744,7 +2744,7 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -2762,7 +2762,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -2812,7 +2812,7 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -2821,7 +2821,7 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -2889,7 +2889,7 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -2898,7 +2898,7 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3049,7 +3049,7 @@
         <v>96</v>
       </c>
       <c r="E4">
-        <v>78.3</v>
+        <v>83.3</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -3067,7 +3067,7 @@
         <v>98</v>
       </c>
       <c r="K4">
-        <v>85.7</v>
+        <v>90</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -3076,7 +3076,7 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O4">
         <v>92.09999999999999</v>
@@ -3085,7 +3085,7 @@
         <v>98</v>
       </c>
       <c r="Q4">
-        <v>85.7</v>
+        <v>93.8</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -3226,7 +3226,7 @@
         <v>80</v>
       </c>
       <c r="E7">
-        <v>78.3</v>
+        <v>75</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -3244,7 +3244,7 @@
         <v>90</v>
       </c>
       <c r="K7">
-        <v>51.4</v>
+        <v>45</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -3253,7 +3253,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>93.8</v>
+        <v>70.8</v>
       </c>
       <c r="O7">
         <v>76.3</v>
@@ -3262,7 +3262,7 @@
         <v>90</v>
       </c>
       <c r="Q7">
-        <v>51.4</v>
+        <v>28.1</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -3371,7 +3371,7 @@
         <v>66.7</v>
       </c>
       <c r="N9">
-        <v>82.8</v>
+        <v>76</v>
       </c>
       <c r="O9">
         <v>76.3</v>
@@ -3380,7 +3380,7 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -3403,7 +3403,7 @@
         <v>84</v>
       </c>
       <c r="E10">
-        <v>78.3</v>
+        <v>83.3</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -3421,7 +3421,7 @@
         <v>92</v>
       </c>
       <c r="K10">
-        <v>85.7</v>
+        <v>90</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -3439,7 +3439,7 @@
         <v>92</v>
       </c>
       <c r="Q10">
-        <v>85.7</v>
+        <v>93.8</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -3489,7 +3489,7 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="O11">
         <v>92.09999999999999</v>
@@ -3548,7 +3548,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O12">
         <v>94.7</v>
@@ -3934,7 +3934,7 @@
         <v>80</v>
       </c>
       <c r="E19">
-        <v>78.3</v>
+        <v>75</v>
       </c>
       <c r="F19">
         <v>100</v>
@@ -3952,7 +3952,7 @@
         <v>90</v>
       </c>
       <c r="K19">
-        <v>51.4</v>
+        <v>45</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -3961,7 +3961,7 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>93.8</v>
+        <v>88.5</v>
       </c>
       <c r="O19">
         <v>76.3</v>
@@ -3970,7 +3970,7 @@
         <v>90</v>
       </c>
       <c r="Q19">
-        <v>51.4</v>
+        <v>37.5</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -4052,7 +4052,7 @@
         <v>80</v>
       </c>
       <c r="E21">
-        <v>78.3</v>
+        <v>75</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -4070,7 +4070,7 @@
         <v>90</v>
       </c>
       <c r="K21">
-        <v>51.4</v>
+        <v>45</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -4079,7 +4079,7 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>90.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="O21">
         <v>73.7</v>
@@ -4088,7 +4088,7 @@
         <v>90</v>
       </c>
       <c r="Q21">
-        <v>51.4</v>
+        <v>28.1</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -4347,7 +4347,7 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>78.3</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -4365,7 +4365,7 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -4383,7 +4383,7 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="R26">
         <v>100</v>
@@ -4433,7 +4433,7 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>93.8</v>
+        <v>88.5</v>
       </c>
       <c r="O27">
         <v>76.3</v>
@@ -4442,7 +4442,7 @@
         <v>90</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -4583,7 +4583,7 @@
         <v>96</v>
       </c>
       <c r="E30">
-        <v>78.3</v>
+        <v>83.3</v>
       </c>
       <c r="F30">
         <v>100</v>
@@ -4601,7 +4601,7 @@
         <v>98</v>
       </c>
       <c r="K30">
-        <v>85.7</v>
+        <v>90</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -4619,7 +4619,7 @@
         <v>98</v>
       </c>
       <c r="Q30">
-        <v>85.7</v>
+        <v>93.8</v>
       </c>
       <c r="R30">
         <v>100</v>
@@ -4642,7 +4642,7 @@
         <v>80</v>
       </c>
       <c r="E31">
-        <v>82.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="F31">
         <v>100</v>
@@ -4660,7 +4660,7 @@
         <v>90</v>
       </c>
       <c r="K31">
-        <v>88.59999999999999</v>
+        <v>90</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -4678,7 +4678,7 @@
         <v>90</v>
       </c>
       <c r="Q31">
-        <v>88.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -4773,7 +4773,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -4794,7 +4794,7 @@
         <v>21.4</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4805,7 +4805,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -4814,19 +4814,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>85.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>14.3</v>
+        <v>17.9</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4837,7 +4837,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -4846,19 +4846,19 @@
         <v>28</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>89.3</v>
+        <v>85.7</v>
       </c>
       <c r="G5" s="2">
-        <v>10.7</v>
+        <v>14.3</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4869,7 +4869,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -4878,19 +4878,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>92.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="G6" s="2">
-        <v>7.1</v>
+        <v>10.7</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4972,7 +4972,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5004,7 +5004,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920239</v>
+        <v>21330051420317</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
@@ -5019,7 +5019,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5027,7 +5027,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920239</v>
+        <v>21330051420317</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -5039,10 +5039,10 @@
         <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920239</v>
+        <v>21330051420317</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -5062,10 +5062,10 @@
         <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5076,19 +5076,19 @@
         <v>21330051420317</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5096,7 +5096,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051420317</v>
+        <v>22330051920231</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -5108,7 +5108,7 @@
         <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>53</v>
@@ -5119,7 +5119,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051420317</v>
+        <v>22330051920231</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
@@ -5131,7 +5131,7 @@
         <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>54</v>
@@ -5145,19 +5145,19 @@
         <v>22330051920231</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5165,7 +5165,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920231</v>
+        <v>22330051920369</v>
       </c>
       <c r="B9" t="s">
         <v>64</v>
@@ -5177,10 +5177,10 @@
         <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5188,16 +5188,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920357</v>
+        <v>22330051920369</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5211,22 +5211,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920357</v>
+        <v>22330051920369</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5234,22 +5234,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920369</v>
+        <v>22330051920366</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920369</v>
+        <v>22330051920366</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5283,19 +5283,19 @@
         <v>22330051920366</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5303,19 +5303,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920366</v>
+        <v>22330051920239</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
         <v>53</v>
@@ -5326,22 +5326,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920253</v>
+        <v>22330051920239</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -5349,16 +5349,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920257</v>
+        <v>22330051920357</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
@@ -5372,24 +5372,93 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
+        <v>22330051920357</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920253</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920257</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
         <v>22330051920401</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B21" t="s">
         <v>70</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C21" t="s">
         <v>79</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D21" t="s">
         <v>88</v>
       </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18">
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>55</v>
+      </c>
+      <c r="G21">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCV - Estadisticos 20241.xlsx
+++ b/grupos/5ALCV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="68">
   <si>
     <t>Materia</t>
   </si>
@@ -176,10 +176,13 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rivera Serra Alma Lilian</t>
+  </si>
+  <si>
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
-    <t>Rivera Serra Alma Lilian</t>
+    <t>Marin Arzaba Roberto</t>
   </si>
   <si>
     <t>Urias Morales Alejandra</t>
@@ -191,9 +194,6 @@
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
-    <t>Marin Arzaba Roberto</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -206,82 +206,19 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>LLANOS</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>GAMBOA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>VALENTE</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>PULIDO</t>
   </si>
   <si>
-    <t>SERGIO</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>AILYN</t>
-  </si>
-  <si>
     <t>CRHIS AMINADAB</t>
-  </si>
-  <si>
-    <t>JARET</t>
-  </si>
-  <si>
-    <t>NOEMI DEL ROCIO</t>
-  </si>
-  <si>
-    <t>KAREN</t>
   </si>
   <si>
     <t>JUAN EMANUEL</t>
@@ -813,10 +750,10 @@
         <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>9</v>
@@ -825,7 +762,7 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>8</v>
@@ -843,7 +780,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -890,10 +827,10 @@
         <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
         <v>9</v>
@@ -902,7 +839,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -967,10 +904,10 @@
         <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -979,7 +916,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1044,10 +981,10 @@
         <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -1056,16 +993,16 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>5</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>5</v>
@@ -1121,10 +1058,10 @@
         <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1133,7 +1070,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1142,7 +1079,7 @@
         <v>7</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1198,10 +1135,10 @@
         <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>5</v>
@@ -1210,7 +1147,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>5</v>
@@ -1275,10 +1212,10 @@
         <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1287,7 +1224,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1296,7 +1233,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1305,7 +1242,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1352,10 +1289,10 @@
         <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
         <v>6</v>
@@ -1364,16 +1301,16 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>9</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1382,7 +1319,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1429,10 +1366,10 @@
         <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>10</v>
@@ -1441,13 +1378,13 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>8</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1506,10 +1443,10 @@
         <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
         <v>9</v>
@@ -1518,7 +1455,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1583,10 +1520,10 @@
         <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>7</v>
@@ -1595,7 +1532,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>5</v>
@@ -1660,10 +1597,10 @@
         <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1672,7 +1609,7 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1737,10 +1674,10 @@
         <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>6</v>
@@ -1749,16 +1686,16 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>6</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -1767,7 +1704,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1814,10 +1751,10 @@
         <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -1826,7 +1763,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -1891,10 +1828,10 @@
         <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -1903,7 +1840,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -1968,10 +1905,10 @@
         <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>5</v>
@@ -1980,7 +1917,7 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>5</v>
@@ -1989,7 +1926,7 @@
         <v>5</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -1998,7 +1935,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2045,10 +1982,10 @@
         <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2057,7 +1994,7 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2122,10 +2059,10 @@
         <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>5</v>
@@ -2134,7 +2071,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
         <v>5</v>
@@ -2143,7 +2080,7 @@
         <v>5</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2152,7 +2089,7 @@
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2199,10 +2136,10 @@
         <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -2211,7 +2148,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2229,7 +2166,7 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2276,10 +2213,10 @@
         <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -2288,13 +2225,13 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>9</v>
@@ -2353,10 +2290,10 @@
         <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -2365,7 +2302,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2430,10 +2367,10 @@
         <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2442,13 +2379,13 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>10</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2460,7 +2397,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2507,10 +2444,10 @@
         <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>9</v>
@@ -2519,13 +2456,13 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>7</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>7</v>
@@ -2584,10 +2521,10 @@
         <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>5</v>
@@ -2596,7 +2533,7 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
         <v>5</v>
@@ -2605,7 +2542,7 @@
         <v>5</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>5</v>
@@ -2614,7 +2551,7 @@
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2661,10 +2598,10 @@
         <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -2673,7 +2610,7 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2738,10 +2675,10 @@
         <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>10</v>
@@ -2750,13 +2687,13 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>9</v>
       </c>
       <c r="U29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2815,10 +2752,10 @@
         <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
         <v>9</v>
@@ -2827,7 +2764,7 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>7</v>
@@ -2892,10 +2829,10 @@
         <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
         <v>8</v>
@@ -2904,7 +2841,7 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -3079,10 +3016,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="O4">
-        <v>92.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="P4">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q4">
         <v>93.8</v>
@@ -3138,10 +3075,10 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>97.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P5">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -3197,7 +3134,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>89.5</v>
+        <v>93.5</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3256,10 +3193,10 @@
         <v>70.8</v>
       </c>
       <c r="O7">
-        <v>76.3</v>
+        <v>50</v>
       </c>
       <c r="P7">
-        <v>90</v>
+        <v>91.3</v>
       </c>
       <c r="Q7">
         <v>28.1</v>
@@ -3268,7 +3205,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>100</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3318,7 +3255,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3374,10 +3311,10 @@
         <v>76</v>
       </c>
       <c r="O9">
-        <v>76.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q9">
         <v>12.5</v>
@@ -3386,7 +3323,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>66.7</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3433,10 +3370,10 @@
         <v>93.8</v>
       </c>
       <c r="O10">
-        <v>78.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P10">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="Q10">
         <v>93.8</v>
@@ -3492,10 +3429,10 @@
         <v>95.8</v>
       </c>
       <c r="O11">
-        <v>92.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="P11">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -3504,7 +3441,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3551,10 +3488,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="O12">
-        <v>94.7</v>
+        <v>93.5</v>
       </c>
       <c r="P12">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -3610,10 +3547,10 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>94.7</v>
+        <v>96.8</v>
       </c>
       <c r="P13">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -3669,10 +3606,10 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>84.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P14">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -3728,10 +3665,10 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>94.7</v>
+        <v>96.8</v>
       </c>
       <c r="P15">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -3787,10 +3724,10 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>86.8</v>
+        <v>88.7</v>
       </c>
       <c r="P16">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -3849,7 +3786,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -3964,7 +3901,7 @@
         <v>88.5</v>
       </c>
       <c r="O19">
-        <v>76.3</v>
+        <v>82.3</v>
       </c>
       <c r="P19">
         <v>90</v>
@@ -3976,7 +3913,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4082,10 +4019,10 @@
         <v>68.8</v>
       </c>
       <c r="O21">
-        <v>73.7</v>
+        <v>48.4</v>
       </c>
       <c r="P21">
-        <v>90</v>
+        <v>91.3</v>
       </c>
       <c r="Q21">
         <v>28.1</v>
@@ -4094,7 +4031,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4141,10 +4078,10 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>92.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="P22">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4200,10 +4137,10 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>97.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P23">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -4318,10 +4255,10 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>94.7</v>
+        <v>96.8</v>
       </c>
       <c r="P25">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -4377,7 +4314,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>92.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -4436,10 +4373,10 @@
         <v>88.5</v>
       </c>
       <c r="O27">
-        <v>76.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="P27">
-        <v>90</v>
+        <v>88.8</v>
       </c>
       <c r="Q27">
         <v>6.3</v>
@@ -4448,7 +4385,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4554,10 +4491,10 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>92.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="P29">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -4613,10 +4550,10 @@
         <v>93.8</v>
       </c>
       <c r="O30">
-        <v>78.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P30">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q30">
         <v>93.8</v>
@@ -4672,10 +4609,10 @@
         <v>100</v>
       </c>
       <c r="O31">
-        <v>97.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P31">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q31">
         <v>93.8</v>
@@ -4741,7 +4678,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>52</v>
@@ -4750,19 +4687,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>75</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>25</v>
+        <v>21.4</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4773,7 +4710,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -4782,19 +4719,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>78.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>21.4</v>
+        <v>17.9</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4805,7 +4742,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -4826,7 +4763,7 @@
         <v>17.9</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4837,7 +4774,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -4846,19 +4783,19 @@
         <v>28</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>85.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>14.3</v>
+        <v>17.9</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4869,7 +4806,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -4878,19 +4815,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>89.3</v>
+        <v>85.7</v>
       </c>
       <c r="G6" s="2">
-        <v>10.7</v>
+        <v>14.3</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4901,7 +4838,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
@@ -4910,19 +4847,19 @@
         <v>28</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>96.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="G7" s="2">
-        <v>3.6</v>
+        <v>14.3</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4972,7 +4909,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5004,22 +4941,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051420317</v>
+        <v>22330051920239</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5027,22 +4964,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051420317</v>
+        <v>22330051920239</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5050,415 +4987,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051420317</v>
+        <v>22330051920401</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051420317</v>
-      </c>
-      <c r="B5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920231</v>
-      </c>
-      <c r="B6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920231</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920231</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920369</v>
-      </c>
-      <c r="B9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920369</v>
-      </c>
-      <c r="B10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920369</v>
-      </c>
-      <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920366</v>
-      </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920366</v>
-      </c>
-      <c r="B13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" t="s">
-        <v>83</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920366</v>
-      </c>
-      <c r="B14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920239</v>
-      </c>
-      <c r="B15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920239</v>
-      </c>
-      <c r="B16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920357</v>
-      </c>
-      <c r="B17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>52</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920357</v>
-      </c>
-      <c r="B18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" t="s">
-        <v>85</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920253</v>
-      </c>
-      <c r="B19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920257</v>
-      </c>
-      <c r="B20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>52</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920401</v>
-      </c>
-      <c r="B21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCV - Estadisticos 20241.xlsx
+++ b/grupos/5ALCV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="65">
   <si>
     <t>Materia</t>
   </si>
@@ -188,12 +188,12 @@
     <t>Urias Morales Alejandra</t>
   </si>
   <si>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Flores Ovalle Victor</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -209,19 +209,10 @@
     <t>GAMBOA</t>
   </si>
   <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
     <t>CRHIS AMINADAB</t>
-  </si>
-  <si>
-    <t>JUAN EMANUEL</t>
   </si>
 </sst>
 </file>
@@ -759,7 +750,7 @@
         <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
         <v>9</v>
@@ -836,7 +827,7 @@
         <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -913,7 +904,7 @@
         <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>10</v>
@@ -990,7 +981,7 @@
         <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
         <v>6</v>
@@ -1067,7 +1058,7 @@
         <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>10</v>
@@ -1144,7 +1135,7 @@
         <v>5</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
         <v>5</v>
@@ -1221,7 +1212,7 @@
         <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>9</v>
@@ -1298,7 +1289,7 @@
         <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>5</v>
@@ -1375,7 +1366,7 @@
         <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
         <v>10</v>
@@ -1452,7 +1443,7 @@
         <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>9</v>
@@ -1529,7 +1520,7 @@
         <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>5</v>
@@ -1606,7 +1597,7 @@
         <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>8</v>
@@ -1624,7 +1615,7 @@
         <v>7</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1683,7 +1674,7 @@
         <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>7</v>
@@ -1760,7 +1751,7 @@
         <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>10</v>
@@ -1837,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>10</v>
@@ -1914,7 +1905,7 @@
         <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>6</v>
@@ -1932,7 +1923,7 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -1991,7 +1982,7 @@
         <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>10</v>
@@ -2068,7 +2059,7 @@
         <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
         <v>6</v>
@@ -2145,7 +2136,7 @@
         <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>9</v>
@@ -2163,7 +2154,7 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2222,7 +2213,7 @@
         <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>10</v>
@@ -2299,7 +2290,7 @@
         <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>10</v>
@@ -2376,7 +2367,7 @@
         <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>8</v>
@@ -2453,7 +2444,7 @@
         <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
         <v>7</v>
@@ -2530,7 +2521,7 @@
         <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
         <v>6</v>
@@ -2607,7 +2598,7 @@
         <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>9</v>
@@ -2684,7 +2675,7 @@
         <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>9</v>
@@ -2761,7 +2752,7 @@
         <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>8</v>
@@ -2779,7 +2770,7 @@
         <v>7</v>
       </c>
       <c r="X30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -2838,7 +2829,7 @@
         <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
         <v>8</v>
@@ -4806,7 +4797,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -4827,7 +4818,7 @@
         <v>14.3</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4838,7 +4829,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
@@ -4847,19 +4838,19 @@
         <v>28</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>85.7</v>
+        <v>89.3</v>
       </c>
       <c r="G7" s="2">
-        <v>14.3</v>
+        <v>10.7</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4909,7 +4900,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4947,10 +4938,10 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="s">
         <v>64</v>
-      </c>
-      <c r="D2" t="s">
-        <v>66</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4970,41 +4961,18 @@
         <v>62</v>
       </c>
       <c r="C3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" t="s">
         <v>64</v>
       </c>
-      <c r="D3" t="s">
-        <v>66</v>
-      </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920401</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4">
         <v>5</v>
       </c>
     </row>
